--- a/Pruebas calificadas/COLEGIO-GIMNASIO-SABIO-CALDAS-(IED)-301_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-GIMNASIO-SABIO-CALDAS-(IED)-301_CALIFICADO.xlsx
@@ -747,11 +747,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -759,7 +755,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -950,11 +946,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -962,7 +954,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1153,11 +1145,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -1165,7 +1153,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1356,11 +1344,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -1368,7 +1352,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1559,11 +1543,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -1571,7 +1551,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1762,11 +1742,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -1774,7 +1750,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1965,11 +1941,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -1977,7 +1949,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2168,11 +2140,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -2180,7 +2148,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2371,11 +2339,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -2383,7 +2347,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2574,11 +2538,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -2586,7 +2546,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2773,11 +2733,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -2785,7 +2741,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2976,11 +2932,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -2988,7 +2940,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3179,11 +3131,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -3191,7 +3139,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -3382,11 +3330,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -3394,7 +3338,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3585,11 +3529,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -3597,7 +3537,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3788,11 +3728,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -3800,7 +3736,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3991,11 +3927,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -4003,7 +3935,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -4194,11 +4126,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -4206,7 +4134,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -4397,11 +4325,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -4409,7 +4333,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -4596,11 +4520,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -4608,7 +4528,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -4799,11 +4719,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -4811,7 +4727,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -5002,11 +4918,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -5014,7 +4926,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -5205,11 +5117,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -5217,7 +5125,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -5408,11 +5316,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -5420,7 +5324,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -5611,11 +5515,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -5623,7 +5523,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -5814,11 +5714,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -5826,7 +5722,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -6017,11 +5913,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -6029,7 +5921,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -6220,11 +6112,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -6232,7 +6120,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -6423,11 +6311,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -6435,7 +6319,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -6614,11 +6498,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -6626,7 +6506,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -6817,11 +6697,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -6829,7 +6705,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -7020,11 +6896,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -7032,7 +6904,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -7219,11 +7091,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -7231,7 +7099,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -7422,11 +7290,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -7434,7 +7298,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -7625,11 +7489,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -7637,7 +7497,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -7828,11 +7688,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -7840,7 +7696,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -8031,11 +7887,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -8043,7 +7895,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -8234,11 +8086,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -8246,7 +8094,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -8437,11 +8285,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -8449,7 +8293,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -8640,11 +8484,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -8652,7 +8492,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -8843,11 +8683,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -8855,7 +8691,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -9046,11 +8882,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -9058,7 +8890,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -9249,11 +9081,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -9261,7 +9089,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -9444,11 +9272,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -9456,7 +9280,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -9643,11 +9467,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -9655,7 +9475,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -9846,11 +9666,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -9858,7 +9674,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -10049,11 +9865,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -10061,7 +9873,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -10252,11 +10064,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -10264,7 +10072,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -10455,11 +10263,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -10467,7 +10271,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -10658,11 +10462,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -10670,7 +10470,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -10861,11 +10661,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -10873,7 +10669,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -11064,11 +10860,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -11076,7 +10868,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -11267,11 +11059,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -11279,7 +11067,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -11470,11 +11258,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -11482,7 +11266,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -11673,11 +11457,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -11685,7 +11465,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -11876,11 +11656,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -11888,7 +11664,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -12079,11 +11855,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -12091,7 +11863,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -12282,11 +12054,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -12294,7 +12062,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -12485,11 +12253,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -12497,7 +12261,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -12684,11 +12448,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -12696,7 +12456,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -12883,11 +12643,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -12895,7 +12651,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -13086,11 +12842,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -13098,7 +12850,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -13289,11 +13041,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -13301,7 +13049,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -13492,11 +13240,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -13504,7 +13248,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -13695,11 +13439,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -13707,7 +13447,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -13898,11 +13638,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -13910,7 +13646,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -14101,11 +13837,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -14113,7 +13845,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -14304,11 +14036,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -14316,7 +14044,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -14507,11 +14235,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -14519,7 +14243,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -14710,11 +14434,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -14722,7 +14442,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -14909,11 +14629,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -14921,7 +14637,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -15112,11 +14828,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -15124,7 +14836,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
